--- a/backend/data/financials_by_company/1JEN.MI.xlsx
+++ b/backend/data/financials_by_company/1JEN.MI.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD5"/>
+  <dimension ref="A1:BD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,224 +702,122 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>91930</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="D2" t="n">
-        <v>220521000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>317000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>317000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>91000000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>74912000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>742639000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>220838000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>145926000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-15148000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>15531000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>766000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>90774930</v>
-      </c>
-      <c r="P2" t="n">
-        <v>92646000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>972204000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1340000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>57238115</v>
-      </c>
-      <c r="T2" t="n">
-        <v>57238115</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W2" t="n">
-        <v>92646000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>92646000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>92646000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-1596000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>94243000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1646000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>92597000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>37798000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>130395000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2389000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>317000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-718000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-1256000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>53000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1604000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-15148000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>383000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>15531000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>766000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>143583000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>229565000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>2315000</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>64023000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>165612000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>103416000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>62196000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1340000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>373148000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>742639000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1115787000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1115787000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>19715000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>19715000</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-5390652</v>
+        <v>-3557424</v>
       </c>
       <c r="C3" t="n">
-        <v>0.337</v>
+        <v>0.208</v>
       </c>
       <c r="D3" t="n">
-        <v>214689000</v>
+        <v>190925000</v>
       </c>
       <c r="E3" t="n">
-        <v>-15996000</v>
+        <v>-17103000</v>
       </c>
       <c r="F3" t="n">
-        <v>-15996000</v>
+        <v>-17103000</v>
       </c>
       <c r="G3" t="n">
-        <v>72816000</v>
+        <v>61917000</v>
       </c>
       <c r="H3" t="n">
-        <v>70870000</v>
+        <v>68265000</v>
       </c>
       <c r="I3" t="n">
-        <v>695527000</v>
+        <v>634981000</v>
       </c>
       <c r="J3" t="n">
-        <v>198693000</v>
+        <v>173822000</v>
       </c>
       <c r="K3" t="n">
-        <v>127823000</v>
+        <v>105557000</v>
       </c>
       <c r="L3" t="n">
-        <v>-15998000</v>
+        <v>-7647000</v>
       </c>
       <c r="M3" t="n">
-        <v>16448000</v>
+        <v>9603000</v>
       </c>
       <c r="N3" t="n">
-        <v>764000</v>
+        <v>875000</v>
       </c>
       <c r="O3" t="n">
-        <v>83421348</v>
+        <v>75462576</v>
       </c>
       <c r="P3" t="n">
-        <v>72466000</v>
+        <v>55100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>924287000</v>
+        <v>861710000</v>
       </c>
       <c r="R3" t="n">
-        <v>937000</v>
+        <v>225000</v>
       </c>
       <c r="S3" t="n">
         <v>57238115</v>
@@ -928,164 +826,164 @@
         <v>57238115</v>
       </c>
       <c r="U3" t="n">
-        <v>1.27</v>
+        <v>0.96</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>0.96</v>
       </c>
       <c r="W3" t="n">
-        <v>72466000</v>
+        <v>55100000</v>
       </c>
       <c r="X3" t="n">
-        <v>72466000</v>
+        <v>55100000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>72466000</v>
+        <v>55100000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-997000</v>
+        <v>-1933000</v>
       </c>
       <c r="AB3" t="n">
-        <v>73462000</v>
+        <v>57034000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-350000</v>
+        <v>-6817000</v>
       </c>
       <c r="AD3" t="n">
-        <v>73812000</v>
+        <v>63851000</v>
       </c>
       <c r="AE3" t="n">
-        <v>37563000</v>
+        <v>32103000</v>
       </c>
       <c r="AF3" t="n">
-        <v>111375000</v>
+        <v>95954000</v>
       </c>
       <c r="AG3" t="n">
-        <v>2693000</v>
+        <v>1314000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-15996000</v>
+        <v>-17103000</v>
       </c>
       <c r="AI3" t="n">
-        <v>2277000</v>
+        <v>-92000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>5005000</v>
+        <v>405000</v>
       </c>
       <c r="AK3" t="n">
-        <v>8714000</v>
+        <v>13894000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>2896000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-15998000</v>
+        <v>-7647000</v>
       </c>
       <c r="AN3" t="n">
-        <v>314000</v>
+        <v>-1081000</v>
       </c>
       <c r="AO3" t="n">
-        <v>16448000</v>
+        <v>9603000</v>
       </c>
       <c r="AP3" t="n">
-        <v>764000</v>
+        <v>875000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>141761000</v>
+        <v>118974000</v>
       </c>
       <c r="AR3" t="n">
-        <v>228760000</v>
+        <v>226729000</v>
       </c>
       <c r="AS3" t="n">
-        <v>2496000</v>
+        <v>2422000</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>60923000</v>
+        <v>54610000</v>
       </c>
       <c r="AW3" t="n">
-        <v>168971000</v>
+        <v>173036000</v>
       </c>
       <c r="AX3" t="n">
-        <v>102984000</v>
+        <v>107559000</v>
       </c>
       <c r="AY3" t="n">
-        <v>65987000</v>
+        <v>65477000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>937000</v>
+        <v>225000</v>
       </c>
       <c r="BA3" t="n">
-        <v>370521000</v>
+        <v>345703000</v>
       </c>
       <c r="BB3" t="n">
-        <v>695527000</v>
+        <v>634981000</v>
       </c>
       <c r="BC3" t="n">
-        <v>1066048000</v>
+        <v>980684000</v>
       </c>
       <c r="BD3" t="n">
-        <v>1066048000</v>
+        <v>980684000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-3557424</v>
+        <v>-5390652</v>
       </c>
       <c r="C4" t="n">
-        <v>0.208</v>
+        <v>0.337</v>
       </c>
       <c r="D4" t="n">
-        <v>190925000</v>
+        <v>214689000</v>
       </c>
       <c r="E4" t="n">
-        <v>-17103000</v>
+        <v>-15996000</v>
       </c>
       <c r="F4" t="n">
-        <v>-17103000</v>
+        <v>-15996000</v>
       </c>
       <c r="G4" t="n">
-        <v>61917000</v>
+        <v>72816000</v>
       </c>
       <c r="H4" t="n">
-        <v>68265000</v>
+        <v>70870000</v>
       </c>
       <c r="I4" t="n">
-        <v>634981000</v>
+        <v>695527000</v>
       </c>
       <c r="J4" t="n">
-        <v>173822000</v>
+        <v>198693000</v>
       </c>
       <c r="K4" t="n">
-        <v>105557000</v>
+        <v>127823000</v>
       </c>
       <c r="L4" t="n">
-        <v>-7647000</v>
+        <v>-15998000</v>
       </c>
       <c r="M4" t="n">
-        <v>9603000</v>
+        <v>16448000</v>
       </c>
       <c r="N4" t="n">
-        <v>875000</v>
+        <v>764000</v>
       </c>
       <c r="O4" t="n">
-        <v>75462576</v>
+        <v>83421348</v>
       </c>
       <c r="P4" t="n">
-        <v>55100000</v>
+        <v>72466000</v>
       </c>
       <c r="Q4" t="n">
-        <v>861710000</v>
+        <v>924287000</v>
       </c>
       <c r="R4" t="n">
-        <v>225000</v>
+        <v>937000</v>
       </c>
       <c r="S4" t="n">
         <v>57238115</v>
@@ -1094,164 +992,164 @@
         <v>57238115</v>
       </c>
       <c r="U4" t="n">
-        <v>0.96</v>
+        <v>1.27</v>
       </c>
       <c r="V4" t="n">
-        <v>0.96</v>
+        <v>1.27</v>
       </c>
       <c r="W4" t="n">
-        <v>55100000</v>
+        <v>72466000</v>
       </c>
       <c r="X4" t="n">
-        <v>55100000</v>
+        <v>72466000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>55100000</v>
+        <v>72466000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1933000</v>
+        <v>-997000</v>
       </c>
       <c r="AB4" t="n">
-        <v>57034000</v>
+        <v>73462000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-6817000</v>
+        <v>-350000</v>
       </c>
       <c r="AD4" t="n">
-        <v>63851000</v>
+        <v>73812000</v>
       </c>
       <c r="AE4" t="n">
-        <v>32103000</v>
+        <v>37563000</v>
       </c>
       <c r="AF4" t="n">
-        <v>95954000</v>
+        <v>111375000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1314000</v>
+        <v>2693000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-17103000</v>
+        <v>-15996000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-92000</v>
+        <v>2277000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>405000</v>
+        <v>5005000</v>
       </c>
       <c r="AK4" t="n">
-        <v>13894000</v>
+        <v>8714000</v>
       </c>
       <c r="AL4" t="n">
-        <v>2896000</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-7647000</v>
+        <v>-15998000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1081000</v>
+        <v>314000</v>
       </c>
       <c r="AO4" t="n">
-        <v>9603000</v>
+        <v>16448000</v>
       </c>
       <c r="AP4" t="n">
-        <v>875000</v>
+        <v>764000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>118974000</v>
+        <v>141761000</v>
       </c>
       <c r="AR4" t="n">
-        <v>226729000</v>
+        <v>228760000</v>
       </c>
       <c r="AS4" t="n">
-        <v>2422000</v>
+        <v>2496000</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>54610000</v>
+        <v>60923000</v>
       </c>
       <c r="AW4" t="n">
-        <v>173036000</v>
+        <v>168971000</v>
       </c>
       <c r="AX4" t="n">
-        <v>107559000</v>
+        <v>102984000</v>
       </c>
       <c r="AY4" t="n">
-        <v>65477000</v>
+        <v>65987000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>225000</v>
+        <v>937000</v>
       </c>
       <c r="BA4" t="n">
-        <v>345703000</v>
+        <v>370521000</v>
       </c>
       <c r="BB4" t="n">
-        <v>634981000</v>
+        <v>695527000</v>
       </c>
       <c r="BC4" t="n">
-        <v>980684000</v>
+        <v>1066048000</v>
       </c>
       <c r="BD4" t="n">
-        <v>980684000</v>
+        <v>1066048000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>3625624</v>
+        <v>91889.76571199999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.136</v>
+        <v>0.289873</v>
       </c>
       <c r="D5" t="n">
-        <v>136028000</v>
+        <v>207516000</v>
       </c>
       <c r="E5" t="n">
-        <v>26659000</v>
+        <v>317000</v>
       </c>
       <c r="F5" t="n">
-        <v>26659000</v>
+        <v>317000</v>
       </c>
       <c r="G5" t="n">
-        <v>90518000</v>
+        <v>91000000</v>
       </c>
       <c r="H5" t="n">
-        <v>54179000</v>
+        <v>74912000</v>
       </c>
       <c r="I5" t="n">
-        <v>493814000</v>
+        <v>742639000</v>
       </c>
       <c r="J5" t="n">
-        <v>162687000</v>
+        <v>207833000</v>
       </c>
       <c r="K5" t="n">
-        <v>108508000</v>
+        <v>132921000</v>
       </c>
       <c r="L5" t="n">
-        <v>-7642000</v>
+        <v>-15148000</v>
       </c>
       <c r="M5" t="n">
-        <v>5960000</v>
+        <v>2526000</v>
       </c>
       <c r="N5" t="n">
-        <v>226000</v>
+        <v>766000</v>
       </c>
       <c r="O5" t="n">
-        <v>67484624</v>
+        <v>90774889.76571199</v>
       </c>
       <c r="P5" t="n">
-        <v>81998000</v>
+        <v>92646000</v>
       </c>
       <c r="Q5" t="n">
-        <v>671337000</v>
+        <v>972204000</v>
       </c>
       <c r="R5" t="n">
-        <v>360000</v>
+        <v>1340000</v>
       </c>
       <c r="S5" t="n">
         <v>57238115</v>
@@ -1260,112 +1158,274 @@
         <v>57238115</v>
       </c>
       <c r="U5" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="V5" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="W5" t="n">
-        <v>81998000</v>
+        <v>92646000</v>
       </c>
       <c r="X5" t="n">
-        <v>81998000</v>
+        <v>92646000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>81998000</v>
+        <v>92646000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-2341000</v>
+        <v>-1596000</v>
       </c>
       <c r="AB5" t="n">
-        <v>84339000</v>
+        <v>94243000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-8520000</v>
+        <v>1646000</v>
       </c>
       <c r="AD5" t="n">
-        <v>92859000</v>
+        <v>92597000</v>
       </c>
       <c r="AE5" t="n">
-        <v>9689000</v>
+        <v>37798000</v>
       </c>
       <c r="AF5" t="n">
-        <v>102548000</v>
+        <v>130395000</v>
       </c>
       <c r="AG5" t="n">
-        <v>1143000</v>
+        <v>2389000</v>
       </c>
       <c r="AH5" t="n">
-        <v>26659000</v>
+        <v>317000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-4693000</v>
+        <v>-718000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1151000</v>
+        <v>-1256000</v>
       </c>
       <c r="AK5" t="n">
-        <v>9000</v>
+        <v>53000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-23126000</v>
+        <v>1604000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-7642000</v>
+        <v>-15148000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1908000</v>
+        <v>13388000</v>
       </c>
       <c r="AO5" t="n">
-        <v>5960000</v>
+        <v>2526000</v>
       </c>
       <c r="AP5" t="n">
-        <v>226000</v>
+        <v>766000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>79380000</v>
+        <v>143583000</v>
       </c>
       <c r="AR5" t="n">
-        <v>177523000</v>
+        <v>229565000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-736000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>19715000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>19715000</v>
-      </c>
+        <v>2315000</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>38886000</v>
+        <v>64023000</v>
       </c>
       <c r="AW5" t="n">
-        <v>143155000</v>
+        <v>165612000</v>
       </c>
       <c r="AX5" t="n">
-        <v>89693000</v>
+        <v>103416000</v>
       </c>
       <c r="AY5" t="n">
-        <v>53462000</v>
+        <v>62196000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>360000</v>
+        <v>1340000</v>
       </c>
       <c r="BA5" t="n">
-        <v>256903000</v>
+        <v>373148000</v>
       </c>
       <c r="BB5" t="n">
-        <v>493814000</v>
+        <v>742639000</v>
       </c>
       <c r="BC5" t="n">
-        <v>750717000</v>
+        <v>1115787000</v>
       </c>
       <c r="BD5" t="n">
-        <v>750717000</v>
+        <v>1115787000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>51258.997558</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.287972</v>
+      </c>
+      <c r="D6" t="n">
+        <v>179520000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>178000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>178000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>68911000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>77192000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>709706000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>179698000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>102506000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-13223000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2590000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>651000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>68784258.997558</v>
+      </c>
+      <c r="P6" t="n">
+        <v>72002000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>934508000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1031000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>57238115</v>
+      </c>
+      <c r="T6" t="n">
+        <v>57238115</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W6" t="n">
+        <v>72002000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>72002000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>72002000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-2231000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>74234000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3091000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>71143000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>28773000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>99916000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2856000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>178000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>157000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-2084000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>744000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1005000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-13223000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>11284000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>2590000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>651000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>111465000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>224802000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1017000</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>61869000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>165607000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>103389000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>62218000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1031000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>336267000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>709706000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1045973000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1045973000</v>
       </c>
     </row>
   </sheetData>
@@ -1379,7 +1439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1781,233 +1841,107 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>57238115</v>
-      </c>
-      <c r="C2" t="n">
-        <v>57238115</v>
-      </c>
-      <c r="D2" t="n">
-        <v>335122000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>481116000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>267565000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1380356000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>327902000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>267565000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>61097000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>960337000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1377255000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>967196000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>6859000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>960337000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>194286000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>148819000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>148819000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>772813000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>511996000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3420000</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>7121000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
-        <v>23011000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>463899000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>46981000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>416918000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>14545000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>260817000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1514000</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="n">
-        <v>17217000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>14116000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>3101000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>13593000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>37358000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>123888000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>3945000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>14348000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>105595000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1740009000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1151290000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4459000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>23780000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7435000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2663000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>2663000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>264000</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="n">
-        <v>692772000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>127820000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>564952000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>419917000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-353815000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>773732000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>31718000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>101634000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>271429000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>368951000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>588719000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1511000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>651000</v>
-      </c>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="n">
-        <v>1885000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>265125000</v>
-      </c>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="n">
-        <v>41596000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>103514000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>120015000</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>94812000</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>7174000</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>130820000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>-4505000</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>135325000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>86741000</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1844000</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>84897000</v>
-      </c>
-      <c r="CB2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>713000</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>543000</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="n">
+        <v>6949000</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="n">
+        <v>14328000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>3638000</v>
+      </c>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="n">
+        <v>156777000</v>
+      </c>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="n">
+        <v>2433000</v>
+      </c>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="n">
+        <v>54817000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>57238115</v>
@@ -2016,40 +1950,40 @@
         <v>57238115</v>
       </c>
       <c r="D3" t="n">
-        <v>358311000</v>
+        <v>425746000</v>
       </c>
       <c r="E3" t="n">
-        <v>490760000</v>
+        <v>536780000</v>
       </c>
       <c r="F3" t="n">
-        <v>184080000</v>
+        <v>101309000</v>
       </c>
       <c r="G3" t="n">
-        <v>896592000</v>
+        <v>1314455000</v>
       </c>
       <c r="H3" t="n">
-        <v>299522000</v>
+        <v>233810000</v>
       </c>
       <c r="I3" t="n">
-        <v>184080000</v>
+        <v>101309000</v>
       </c>
       <c r="J3" t="n">
-        <v>64759000</v>
+        <v>54276000</v>
       </c>
       <c r="K3" t="n">
-        <v>896592000</v>
+        <v>831951000</v>
       </c>
       <c r="L3" t="n">
-        <v>896592000</v>
+        <v>1267320000</v>
       </c>
       <c r="M3" t="n">
-        <v>903312000</v>
+        <v>843307000</v>
       </c>
       <c r="N3" t="n">
-        <v>6720000</v>
+        <v>11356000</v>
       </c>
       <c r="O3" t="n">
-        <v>896592000</v>
+        <v>831951000</v>
       </c>
       <c r="P3" t="n">
         <v>194286000</v>
@@ -2061,181 +1995,189 @@
         <v>148819000</v>
       </c>
       <c r="S3" t="n">
-        <v>763600000</v>
+        <v>828458000</v>
       </c>
       <c r="T3" t="n">
-        <v>496035000</v>
+        <v>518959000</v>
       </c>
       <c r="U3" t="n">
-        <v>1937000</v>
+        <v>3863000</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>4627000</v>
+        <v>4262000</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>2891000</v>
+        <v>16062000</v>
       </c>
       <c r="Z3" t="n">
-        <v>472323000</v>
+        <v>477729000</v>
       </c>
       <c r="AA3" t="n">
-        <v>50479000</v>
+        <v>42360000</v>
       </c>
       <c r="AB3" t="n">
-        <v>416008000</v>
+        <v>435369000</v>
       </c>
       <c r="AC3" t="n">
-        <v>14257000</v>
+        <v>17043000</v>
       </c>
       <c r="AD3" t="n">
-        <v>267565000</v>
+        <v>309499000</v>
       </c>
       <c r="AE3" t="n">
-        <v>1365000</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+        <v>1293000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>10921000</v>
+      </c>
       <c r="AG3" t="n">
-        <v>18437000</v>
+        <v>59051000</v>
       </c>
       <c r="AH3" t="n">
-        <v>14280000</v>
+        <v>11916000</v>
       </c>
       <c r="AI3" t="n">
-        <v>9993000</v>
+        <v>47135000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>12109000</v>
+        <v>11025000</v>
       </c>
       <c r="AK3" t="n">
-        <v>37815000</v>
+        <v>43887000</v>
       </c>
       <c r="AL3" t="n">
-        <v>126011000</v>
+        <v>122843000</v>
       </c>
       <c r="AM3" t="n">
-        <v>4630000</v>
+        <v>3762000</v>
       </c>
       <c r="AN3" t="n">
-        <v>12571000</v>
+        <v>18481000</v>
       </c>
       <c r="AO3" t="n">
-        <v>108810000</v>
+        <v>100600000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1666912000</v>
+        <v>1671765000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1099825000</v>
+        <v>1128455000</v>
       </c>
       <c r="AR3" t="n">
-        <v>1575000</v>
+        <v>1057000</v>
       </c>
       <c r="AS3" t="n">
-        <v>9182000</v>
+        <v>38822000</v>
       </c>
       <c r="AT3" t="n">
-        <v>8086000</v>
+        <v>10428000</v>
       </c>
       <c r="AU3" t="n">
-        <v>3148000</v>
+        <v>4996000</v>
       </c>
       <c r="AV3" t="n">
-        <v>3148000</v>
+        <v>4996000</v>
       </c>
       <c r="AW3" t="n">
-        <v>207000</v>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+        <v>14310000</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>14310000</v>
+      </c>
       <c r="AY3" t="n">
-        <v>3461000</v>
+        <v>3592000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>712512000</v>
+        <v>730642000</v>
       </c>
       <c r="BA3" t="n">
-        <v>146138000</v>
+        <v>163638000</v>
       </c>
       <c r="BB3" t="n">
-        <v>566374000</v>
+        <v>567004000</v>
       </c>
       <c r="BC3" t="n">
-        <v>365115000</v>
+        <v>324606000</v>
       </c>
       <c r="BD3" t="n">
-        <v>-319548000</v>
+        <v>-288752000</v>
       </c>
       <c r="BE3" t="n">
-        <v>681202000</v>
+        <v>613358000</v>
       </c>
       <c r="BF3" t="n">
-        <v>52134000</v>
+        <v>35857000</v>
       </c>
       <c r="BG3" t="n">
-        <v>104766000</v>
+        <v>97606000</v>
       </c>
       <c r="BH3" t="n">
-        <v>248023000</v>
+        <v>207779000</v>
       </c>
       <c r="BI3" t="n">
-        <v>276279000</v>
+        <v>272116000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>567087000</v>
+        <v>543309000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1477000</v>
+        <v>636000</v>
       </c>
       <c r="BL3" t="n">
-        <v>1598000</v>
-      </c>
-      <c r="BM3" t="inlineStr"/>
+        <v>1385000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0</v>
+      </c>
       <c r="BN3" t="n">
-        <v>2578000</v>
+        <v>1838000</v>
       </c>
       <c r="BO3" t="n">
-        <v>266683000</v>
-      </c>
-      <c r="BP3" t="inlineStr"/>
+        <v>254111000</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1838000</v>
+      </c>
       <c r="BQ3" t="n">
-        <v>40262000</v>
+        <v>35689000</v>
       </c>
       <c r="BR3" t="n">
-        <v>118789000</v>
+        <v>112626000</v>
       </c>
       <c r="BS3" t="n">
-        <v>107632000</v>
+        <v>105796000</v>
       </c>
       <c r="BT3" t="n">
-        <v>76418000</v>
+        <v>77578000</v>
       </c>
       <c r="BU3" t="n">
-        <v>4354000</v>
+        <v>9899000</v>
       </c>
       <c r="BV3" t="n">
-        <v>144240000</v>
+        <v>138769000</v>
       </c>
       <c r="BW3" t="n">
-        <v>-6257000</v>
+        <v>-7194000</v>
       </c>
       <c r="BX3" t="n">
-        <v>150497000</v>
+        <v>145963000</v>
       </c>
       <c r="BY3" t="n">
-        <v>69739000</v>
+        <v>59093000</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2049000</v>
+        <v>2335000</v>
       </c>
       <c r="CA3" t="n">
-        <v>67690000</v>
+        <v>56758000</v>
       </c>
       <c r="CB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>57238115</v>
@@ -2244,40 +2186,40 @@
         <v>57238115</v>
       </c>
       <c r="D4" t="n">
-        <v>425746000</v>
+        <v>358311000</v>
       </c>
       <c r="E4" t="n">
-        <v>536780000</v>
+        <v>490760000</v>
       </c>
       <c r="F4" t="n">
-        <v>101309000</v>
+        <v>184080000</v>
       </c>
       <c r="G4" t="n">
-        <v>1314455000</v>
+        <v>896592000</v>
       </c>
       <c r="H4" t="n">
-        <v>233810000</v>
+        <v>299522000</v>
       </c>
       <c r="I4" t="n">
-        <v>101309000</v>
+        <v>184080000</v>
       </c>
       <c r="J4" t="n">
-        <v>54276000</v>
+        <v>64759000</v>
       </c>
       <c r="K4" t="n">
-        <v>831951000</v>
+        <v>896592000</v>
       </c>
       <c r="L4" t="n">
-        <v>1267320000</v>
+        <v>896592000</v>
       </c>
       <c r="M4" t="n">
-        <v>843307000</v>
+        <v>903312000</v>
       </c>
       <c r="N4" t="n">
-        <v>11356000</v>
+        <v>6720000</v>
       </c>
       <c r="O4" t="n">
-        <v>831951000</v>
+        <v>896592000</v>
       </c>
       <c r="P4" t="n">
         <v>194286000</v>
@@ -2289,189 +2231,181 @@
         <v>148819000</v>
       </c>
       <c r="S4" t="n">
-        <v>828458000</v>
+        <v>763600000</v>
       </c>
       <c r="T4" t="n">
-        <v>518959000</v>
+        <v>496035000</v>
       </c>
       <c r="U4" t="n">
-        <v>3863000</v>
+        <v>1937000</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>4262000</v>
+        <v>4627000</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>16062000</v>
+        <v>2891000</v>
       </c>
       <c r="Z4" t="n">
-        <v>477729000</v>
+        <v>472323000</v>
       </c>
       <c r="AA4" t="n">
-        <v>42360000</v>
+        <v>50479000</v>
       </c>
       <c r="AB4" t="n">
-        <v>435369000</v>
+        <v>416008000</v>
       </c>
       <c r="AC4" t="n">
-        <v>17043000</v>
+        <v>14257000</v>
       </c>
       <c r="AD4" t="n">
-        <v>309499000</v>
+        <v>267565000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1293000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>10921000</v>
-      </c>
+        <v>1365000</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>59051000</v>
+        <v>18437000</v>
       </c>
       <c r="AH4" t="n">
-        <v>11916000</v>
+        <v>14280000</v>
       </c>
       <c r="AI4" t="n">
-        <v>47135000</v>
+        <v>9993000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11025000</v>
+        <v>12109000</v>
       </c>
       <c r="AK4" t="n">
-        <v>43887000</v>
+        <v>37815000</v>
       </c>
       <c r="AL4" t="n">
-        <v>122843000</v>
+        <v>126011000</v>
       </c>
       <c r="AM4" t="n">
-        <v>3762000</v>
+        <v>4630000</v>
       </c>
       <c r="AN4" t="n">
-        <v>18481000</v>
+        <v>12571000</v>
       </c>
       <c r="AO4" t="n">
-        <v>100600000</v>
+        <v>108810000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1671765000</v>
+        <v>1666912000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1128455000</v>
+        <v>1099825000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1057000</v>
+        <v>1575000</v>
       </c>
       <c r="AS4" t="n">
-        <v>38822000</v>
+        <v>9182000</v>
       </c>
       <c r="AT4" t="n">
-        <v>10428000</v>
+        <v>8086000</v>
       </c>
       <c r="AU4" t="n">
-        <v>4996000</v>
+        <v>3148000</v>
       </c>
       <c r="AV4" t="n">
-        <v>4996000</v>
+        <v>3148000</v>
       </c>
       <c r="AW4" t="n">
-        <v>14310000</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>14310000</v>
-      </c>
+        <v>207000</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
-        <v>3592000</v>
+        <v>3461000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>730642000</v>
+        <v>712512000</v>
       </c>
       <c r="BA4" t="n">
-        <v>163638000</v>
+        <v>146138000</v>
       </c>
       <c r="BB4" t="n">
-        <v>567004000</v>
+        <v>566374000</v>
       </c>
       <c r="BC4" t="n">
-        <v>324606000</v>
+        <v>365115000</v>
       </c>
       <c r="BD4" t="n">
-        <v>-288752000</v>
+        <v>-319548000</v>
       </c>
       <c r="BE4" t="n">
-        <v>613358000</v>
+        <v>681202000</v>
       </c>
       <c r="BF4" t="n">
-        <v>35857000</v>
+        <v>52134000</v>
       </c>
       <c r="BG4" t="n">
-        <v>97606000</v>
+        <v>104766000</v>
       </c>
       <c r="BH4" t="n">
-        <v>207779000</v>
+        <v>248023000</v>
       </c>
       <c r="BI4" t="n">
-        <v>272116000</v>
+        <v>276279000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>543309000</v>
+        <v>567087000</v>
       </c>
       <c r="BK4" t="n">
-        <v>636000</v>
+        <v>1477000</v>
       </c>
       <c r="BL4" t="n">
-        <v>1385000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0</v>
-      </c>
+        <v>1598000</v>
+      </c>
+      <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="n">
-        <v>1838000</v>
+        <v>2578000</v>
       </c>
       <c r="BO4" t="n">
-        <v>254111000</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1838000</v>
-      </c>
+        <v>266683000</v>
+      </c>
+      <c r="BP4" t="inlineStr"/>
       <c r="BQ4" t="n">
-        <v>35689000</v>
+        <v>40262000</v>
       </c>
       <c r="BR4" t="n">
-        <v>112626000</v>
+        <v>118789000</v>
       </c>
       <c r="BS4" t="n">
-        <v>105796000</v>
+        <v>107632000</v>
       </c>
       <c r="BT4" t="n">
-        <v>77578000</v>
+        <v>76418000</v>
       </c>
       <c r="BU4" t="n">
-        <v>9899000</v>
+        <v>4354000</v>
       </c>
       <c r="BV4" t="n">
-        <v>138769000</v>
+        <v>144240000</v>
       </c>
       <c r="BW4" t="n">
-        <v>-7194000</v>
+        <v>-6257000</v>
       </c>
       <c r="BX4" t="n">
-        <v>145963000</v>
+        <v>150497000</v>
       </c>
       <c r="BY4" t="n">
-        <v>59093000</v>
+        <v>69739000</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2335000</v>
+        <v>2049000</v>
       </c>
       <c r="CA4" t="n">
-        <v>56758000</v>
+        <v>67690000</v>
       </c>
       <c r="CB4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>57238115</v>
@@ -2480,40 +2414,40 @@
         <v>57238115</v>
       </c>
       <c r="D5" t="n">
-        <v>503976000</v>
+        <v>335122000</v>
       </c>
       <c r="E5" t="n">
-        <v>597739000</v>
+        <v>481116000</v>
       </c>
       <c r="F5" t="n">
-        <v>14563000</v>
+        <v>267565000</v>
       </c>
       <c r="G5" t="n">
-        <v>1326603000</v>
+        <v>1380356000</v>
       </c>
       <c r="H5" t="n">
-        <v>172992000</v>
+        <v>327902000</v>
       </c>
       <c r="I5" t="n">
-        <v>14563000</v>
+        <v>267565000</v>
       </c>
       <c r="J5" t="n">
-        <v>38946000</v>
+        <v>61097000</v>
       </c>
       <c r="K5" t="n">
-        <v>767810000</v>
+        <v>960337000</v>
       </c>
       <c r="L5" t="n">
-        <v>1189028000</v>
+        <v>1377255000</v>
       </c>
       <c r="M5" t="n">
-        <v>780659000</v>
+        <v>967196000</v>
       </c>
       <c r="N5" t="n">
-        <v>12849000</v>
+        <v>6859000</v>
       </c>
       <c r="O5" t="n">
-        <v>767810000</v>
+        <v>960337000</v>
       </c>
       <c r="P5" t="n">
         <v>194286000</v>
@@ -2525,189 +2459,401 @@
         <v>148819000</v>
       </c>
       <c r="S5" t="n">
-        <v>976382000</v>
+        <v>772813000</v>
       </c>
       <c r="T5" t="n">
-        <v>503103000</v>
+        <v>511996000</v>
       </c>
       <c r="U5" t="n">
-        <v>2351000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>713000</v>
-      </c>
+        <v>3420000</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>9379000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>543000</v>
-      </c>
+        <v>7121000</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>24741000</v>
+        <v>23011000</v>
       </c>
       <c r="Z5" t="n">
-        <v>448746000</v>
+        <v>463899000</v>
       </c>
       <c r="AA5" t="n">
-        <v>27528000</v>
+        <v>46981000</v>
       </c>
       <c r="AB5" t="n">
-        <v>421218000</v>
+        <v>416918000</v>
       </c>
       <c r="AC5" t="n">
-        <v>17886000</v>
+        <v>14545000</v>
       </c>
       <c r="AD5" t="n">
-        <v>473279000</v>
+        <v>260817000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1979000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>6949000</v>
-      </c>
+        <v>1514000</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>148993000</v>
+        <v>17217000</v>
       </c>
       <c r="AH5" t="n">
-        <v>11418000</v>
+        <v>14116000</v>
       </c>
       <c r="AI5" t="n">
-        <v>137575000</v>
+        <v>3101000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>11100000</v>
+        <v>13593000</v>
       </c>
       <c r="AK5" t="n">
-        <v>39907000</v>
+        <v>37358000</v>
       </c>
       <c r="AL5" t="n">
-        <v>111238000</v>
+        <v>123888000</v>
       </c>
       <c r="AM5" t="n">
-        <v>2897000</v>
+        <v>3945000</v>
       </c>
       <c r="AN5" t="n">
-        <v>14120000</v>
+        <v>14348000</v>
       </c>
       <c r="AO5" t="n">
-        <v>94221000</v>
+        <v>105595000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1757041000</v>
+        <v>1740009000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1110770000</v>
+        <v>1151290000</v>
       </c>
       <c r="AR5" t="n">
-        <v>1604000</v>
+        <v>4459000</v>
       </c>
       <c r="AS5" t="n">
-        <v>63360000</v>
+        <v>23780000</v>
       </c>
       <c r="AT5" t="n">
-        <v>2978000</v>
+        <v>7435000</v>
       </c>
       <c r="AU5" t="n">
-        <v>4957000</v>
+        <v>2663000</v>
       </c>
       <c r="AV5" t="n">
-        <v>4957000</v>
+        <v>2663000</v>
       </c>
       <c r="AW5" t="n">
-        <v>14328000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>14328000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3638000</v>
-      </c>
+        <v>264000</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>753247000</v>
+        <v>692772000</v>
       </c>
       <c r="BA5" t="n">
-        <v>180224000</v>
+        <v>127820000</v>
       </c>
       <c r="BB5" t="n">
-        <v>573023000</v>
+        <v>564952000</v>
       </c>
       <c r="BC5" t="n">
-        <v>266656000</v>
+        <v>419917000</v>
       </c>
       <c r="BD5" t="n">
-        <v>-273491000</v>
+        <v>-353815000</v>
       </c>
       <c r="BE5" t="n">
-        <v>540146000</v>
+        <v>773732000</v>
       </c>
       <c r="BF5" t="n">
-        <v>18424000</v>
+        <v>31718000</v>
       </c>
       <c r="BG5" t="n">
-        <v>95304000</v>
+        <v>101634000</v>
       </c>
       <c r="BH5" t="n">
-        <v>187949000</v>
+        <v>271429000</v>
       </c>
       <c r="BI5" t="n">
-        <v>238469000</v>
+        <v>368951000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>646271000</v>
+        <v>588719000</v>
       </c>
       <c r="BK5" t="n">
-        <v>811000</v>
+        <v>1511000</v>
       </c>
       <c r="BL5" t="n">
-        <v>68000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>156777000</v>
-      </c>
-      <c r="BN5" t="inlineStr"/>
+        <v>651000</v>
+      </c>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="n">
+        <v>1885000</v>
+      </c>
       <c r="BO5" t="n">
-        <v>200213000</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>2433000</v>
-      </c>
+        <v>265125000</v>
+      </c>
+      <c r="BP5" t="inlineStr"/>
       <c r="BQ5" t="n">
-        <v>30285000</v>
+        <v>41596000</v>
       </c>
       <c r="BR5" t="n">
-        <v>86840000</v>
+        <v>103514000</v>
       </c>
       <c r="BS5" t="n">
-        <v>80655000</v>
+        <v>120015000</v>
       </c>
       <c r="BT5" t="n">
-        <v>105437000</v>
+        <v>94812000</v>
       </c>
       <c r="BU5" t="n">
-        <v>4918000</v>
+        <v>7174000</v>
       </c>
       <c r="BV5" t="n">
-        <v>120474000</v>
+        <v>130820000</v>
       </c>
       <c r="BW5" t="n">
-        <v>-6750000</v>
+        <v>-4505000</v>
       </c>
       <c r="BX5" t="n">
-        <v>127224000</v>
+        <v>135325000</v>
       </c>
       <c r="BY5" t="n">
-        <v>57573000</v>
+        <v>86741000</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2756000</v>
+        <v>1844000</v>
       </c>
       <c r="CA5" t="n">
-        <v>54817000</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>54817000</v>
-      </c>
+        <v>84897000</v>
+      </c>
+      <c r="CB5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57238115</v>
+      </c>
+      <c r="C6" t="n">
+        <v>57238115</v>
+      </c>
+      <c r="D6" t="n">
+        <v>254146000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>401204000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>332501000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1338784000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>207703000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>332501000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>65342000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1002922000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1226617000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1009559000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6637000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1002922000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>194286000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>148819000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>148819000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>666981000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>320764000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1241000</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>4308000</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>27451000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>274027000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>50332000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>223695000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>13737000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>346217000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1557000</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="n">
+        <v>127177000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>15010000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>112167000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>22756000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>30289000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>107784000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2808000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>13449000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>91527000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1676540000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1122620000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>3728000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>19701000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>84000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2276000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2276000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>214000</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>670421000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>111005000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>559416000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>426196000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-378469000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>804665000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>17064000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>101341000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>305709000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>380551000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>553920000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1457000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1706000</v>
+      </c>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="n">
+        <v>3318000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>233289000</v>
+      </c>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="n">
+        <v>31192000</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>97138000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>104959000</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>93191000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>7793000</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>128320000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>-1858000</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>130178000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>84846000</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>3130000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>81716000</v>
+      </c>
+      <c r="CB6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2720,7 +2866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL5"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2912,454 +3058,496 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>73120000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-23468000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-94000000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>84897000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>92000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>67690000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>409000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>16706000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-62385000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>14300000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-16447000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-20033000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-23468000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-23468000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-23468000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-88029000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>623000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>248000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>248000</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>2031000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2031000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
-        <v>3069000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3069000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-94000000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>167120000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-25858000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-29043000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-27893000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>16109000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>74912000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>74912000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="n">
-        <v>132041000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>-2183000</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>-379963000</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="n">
+        <v>-3858000</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>77934000</v>
+        <v>63457000</v>
       </c>
       <c r="C3" t="n">
-        <v>-68076000</v>
+        <v>-206783000</v>
       </c>
       <c r="D3" t="n">
-        <v>-89057000</v>
+        <v>-79250000</v>
       </c>
       <c r="E3" t="n">
-        <v>67690000</v>
+        <v>56758000</v>
       </c>
       <c r="F3" t="n">
-        <v>-120000</v>
+        <v>-62000</v>
       </c>
       <c r="G3" t="n">
-        <v>56758000</v>
+        <v>54817000</v>
       </c>
       <c r="H3" t="n">
-        <v>-2518000</v>
+        <v>36000</v>
       </c>
       <c r="I3" t="n">
-        <v>13570000</v>
+        <v>1967000</v>
       </c>
       <c r="J3" t="n">
-        <v>-104940000</v>
+        <v>-127325000</v>
       </c>
       <c r="K3" t="n">
-        <v>14329000</v>
+        <v>122249000</v>
       </c>
       <c r="L3" t="n">
-        <v>-15697000</v>
+        <v>-10544000</v>
       </c>
       <c r="M3" t="n">
-        <v>-17171000</v>
+        <v>-14310000</v>
       </c>
       <c r="N3" t="n">
-        <v>-68076000</v>
+        <v>-206783000</v>
       </c>
       <c r="O3" t="n">
-        <v>-68076000</v>
+        <v>-206783000</v>
       </c>
       <c r="P3" t="n">
-        <v>-68076000</v>
+        <v>-206783000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-48481000</v>
+        <v>-13415000</v>
       </c>
       <c r="R3" t="n">
         <v>-1000</v>
       </c>
       <c r="S3" t="n">
-        <v>988000</v>
+        <v>233000</v>
       </c>
       <c r="T3" t="n">
-        <v>3967000</v>
+        <v>344000</v>
       </c>
       <c r="U3" t="n">
-        <v>3967000</v>
+        <v>1583000</v>
       </c>
       <c r="V3" t="n">
-        <v>-1377000</v>
+        <v>-1239000</v>
       </c>
       <c r="W3" t="n">
-        <v>14254000</v>
+        <v>63879000</v>
       </c>
       <c r="X3" t="n">
-        <v>14254000</v>
+        <v>63879000</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>21368000</v>
+        <v>1380000</v>
       </c>
       <c r="AA3" t="n">
-        <v>21368000</v>
+        <v>1380000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-89057000</v>
+        <v>-79250000</v>
       </c>
       <c r="AC3" t="n">
-        <v>166991000</v>
+        <v>142707000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-26665000</v>
+        <v>-14761000</v>
       </c>
       <c r="AE3" t="n">
-        <v>95000</v>
+        <v>720000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-19582000</v>
+        <v>-27773000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-12556000</v>
+        <v>-27262000</v>
       </c>
       <c r="AH3" t="n">
-        <v>14438000</v>
+        <v>6859000</v>
       </c>
       <c r="AI3" t="n">
-        <v>70870000</v>
+        <v>68265000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>70870000</v>
+        <v>68265000</v>
       </c>
       <c r="AK3" t="n">
-        <v>4415000</v>
+        <v>4893000</v>
       </c>
       <c r="AL3" t="n">
-        <v>111026000</v>
+        <v>90612000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>63457000</v>
+        <v>77934000</v>
       </c>
       <c r="C4" t="n">
-        <v>-206783000</v>
+        <v>-68076000</v>
       </c>
       <c r="D4" t="n">
-        <v>-79250000</v>
+        <v>-89057000</v>
       </c>
       <c r="E4" t="n">
+        <v>67690000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-120000</v>
+      </c>
+      <c r="G4" t="n">
         <v>56758000</v>
       </c>
-      <c r="F4" t="n">
-        <v>-62000</v>
-      </c>
-      <c r="G4" t="n">
-        <v>54817000</v>
-      </c>
       <c r="H4" t="n">
-        <v>36000</v>
+        <v>-2518000</v>
       </c>
       <c r="I4" t="n">
-        <v>1967000</v>
+        <v>13570000</v>
       </c>
       <c r="J4" t="n">
-        <v>-127325000</v>
+        <v>-104940000</v>
       </c>
       <c r="K4" t="n">
-        <v>122249000</v>
+        <v>14329000</v>
       </c>
       <c r="L4" t="n">
-        <v>-10544000</v>
+        <v>-15697000</v>
       </c>
       <c r="M4" t="n">
-        <v>-14310000</v>
+        <v>-17171000</v>
       </c>
       <c r="N4" t="n">
-        <v>-206783000</v>
+        <v>-68076000</v>
       </c>
       <c r="O4" t="n">
-        <v>-206783000</v>
+        <v>-68076000</v>
       </c>
       <c r="P4" t="n">
-        <v>-206783000</v>
+        <v>-68076000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-13415000</v>
+        <v>-48481000</v>
       </c>
       <c r="R4" t="n">
         <v>-1000</v>
       </c>
       <c r="S4" t="n">
-        <v>233000</v>
+        <v>988000</v>
       </c>
       <c r="T4" t="n">
-        <v>344000</v>
+        <v>3967000</v>
       </c>
       <c r="U4" t="n">
-        <v>1583000</v>
+        <v>3967000</v>
       </c>
       <c r="V4" t="n">
-        <v>-1239000</v>
+        <v>-1377000</v>
       </c>
       <c r="W4" t="n">
-        <v>63879000</v>
+        <v>14254000</v>
       </c>
       <c r="X4" t="n">
-        <v>63879000</v>
+        <v>14254000</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>1380000</v>
+        <v>21368000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1380000</v>
+        <v>21368000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-79250000</v>
+        <v>-89057000</v>
       </c>
       <c r="AC4" t="n">
-        <v>142707000</v>
+        <v>166991000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-14761000</v>
+        <v>-26665000</v>
       </c>
       <c r="AE4" t="n">
-        <v>720000</v>
+        <v>95000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-27773000</v>
+        <v>-19582000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-27262000</v>
+        <v>-12556000</v>
       </c>
       <c r="AH4" t="n">
-        <v>6859000</v>
+        <v>14438000</v>
       </c>
       <c r="AI4" t="n">
-        <v>68265000</v>
+        <v>70870000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>68265000</v>
+        <v>70870000</v>
       </c>
       <c r="AK4" t="n">
-        <v>4893000</v>
+        <v>4415000</v>
       </c>
       <c r="AL4" t="n">
-        <v>90612000</v>
+        <v>111026000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>51871000</v>
+        <v>73120000</v>
       </c>
       <c r="C5" t="n">
-        <v>-208088000</v>
+        <v>-23468000</v>
       </c>
       <c r="D5" t="n">
-        <v>-46163000</v>
+        <v>-94000000</v>
       </c>
       <c r="E5" t="n">
-        <v>54817000</v>
+        <v>84897000</v>
       </c>
       <c r="F5" t="n">
-        <v>-77000</v>
+        <v>92000</v>
       </c>
       <c r="G5" t="n">
-        <v>63405000</v>
+        <v>67690000</v>
       </c>
       <c r="H5" t="n">
-        <v>2871000</v>
+        <v>409000</v>
       </c>
       <c r="I5" t="n">
-        <v>-11382000</v>
+        <v>16706000</v>
       </c>
       <c r="J5" t="n">
-        <v>304205000</v>
+        <v>-62385000</v>
       </c>
       <c r="K5" t="n">
-        <v>549504000</v>
+        <v>14300000</v>
       </c>
       <c r="L5" t="n">
-        <v>-7420000</v>
+        <v>-16447000</v>
       </c>
       <c r="M5" t="n">
-        <v>-14310000</v>
+        <v>-20033000</v>
       </c>
       <c r="N5" t="n">
-        <v>-208088000</v>
+        <v>-23468000</v>
       </c>
       <c r="O5" t="n">
-        <v>-208088000</v>
+        <v>-23468000</v>
       </c>
       <c r="P5" t="n">
-        <v>-208088000</v>
+        <v>-23468000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-413621000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-1000</v>
-      </c>
+        <v>-88029000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>184000</v>
+        <v>623000</v>
       </c>
       <c r="T5" t="n">
-        <v>4050000</v>
+        <v>248000</v>
       </c>
       <c r="U5" t="n">
-        <v>6233000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-2183000</v>
-      </c>
+        <v>248000</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>-372377000</v>
+        <v>2031000</v>
       </c>
       <c r="X5" t="n">
-        <v>7586000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-379963000</v>
-      </c>
+        <v>2031000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>686000</v>
+        <v>3069000</v>
       </c>
       <c r="AA5" t="n">
-        <v>686000</v>
+        <v>3069000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-46163000</v>
+        <v>-94000000</v>
       </c>
       <c r="AC5" t="n">
-        <v>98034000</v>
+        <v>167120000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-10237000</v>
+        <v>-25858000</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-32428000</v>
+        <v>-29043000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-34066000</v>
+        <v>-27893000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-26297000</v>
+        <v>16109000</v>
       </c>
       <c r="AI5" t="n">
-        <v>54179000</v>
+        <v>74912000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>54179000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-3858000</v>
-      </c>
+        <v>74912000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>94318000</v>
+        <v>132041000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>121169000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-97755000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-74869000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>81716000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>38000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>84897000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-5727000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2508000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-123911000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27561000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-14002000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-21750000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-97755000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-97755000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-97755000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-69619000</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>598000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>677000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>677000</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>2875000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2875000</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-74869000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>196038000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-27827000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>30136000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>37402000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>14938000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>77192000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>77192000</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="n">
+        <v>103006000</v>
       </c>
     </row>
   </sheetData>
@@ -3929,197 +4117,197 @@
       </c>
       <c r="DG1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="EP1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>shortName</t>
         </is>
       </c>
       <c r="ET1" t="inlineStr">
@@ -4139,10 +4327,8 @@
           <t>Jena</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>07743</t>
-        </is>
+      <c r="C2" t="n">
+        <v>7743</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4218,7 +4404,7 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="V2" t="n">
         <v>1767139200</v>
@@ -4235,100 +4421,100 @@
         <v>2</v>
       </c>
       <c r="Z2" t="n">
-        <v>45.72</v>
+        <v>45.12</v>
       </c>
       <c r="AA2" t="n">
-        <v>47.06</v>
+        <v>45.28</v>
       </c>
       <c r="AB2" t="n">
-        <v>47.06</v>
+        <v>45.28</v>
       </c>
       <c r="AC2" t="n">
-        <v>47.06</v>
+        <v>45.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>45.72</v>
+        <v>45.12</v>
       </c>
       <c r="AE2" t="n">
-        <v>47.06</v>
+        <v>45.28</v>
       </c>
       <c r="AF2" t="n">
-        <v>47.06</v>
+        <v>45.28</v>
       </c>
       <c r="AG2" t="n">
-        <v>47.06</v>
+        <v>45.28</v>
       </c>
       <c r="AH2" t="n">
         <v>0.4</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="AJ2" t="n">
         <v>1781049600</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.3193</v>
+        <v>0.2857</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.184</v>
+        <v>1.259</v>
       </c>
       <c r="AM2" t="n">
-        <v>39.63025</v>
+        <v>34.827065</v>
       </c>
       <c r="AN2" t="n">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="AO2" t="n">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="AP2" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AQ2" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AR2" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AS2" t="n">
-        <v>47</v>
+        <v>46.14</v>
       </c>
       <c r="AT2" t="n">
-        <v>47.4</v>
+        <v>46.54</v>
       </c>
       <c r="AU2" t="n">
-        <v>2699349504</v>
+        <v>2651269632</v>
       </c>
       <c r="AV2" t="n">
-        <v>2627229478</v>
+        <v>2519621822</v>
       </c>
       <c r="AW2" t="n">
         <v>16.33</v>
       </c>
       <c r="AX2" t="n">
-        <v>47.06</v>
+        <v>47.94</v>
       </c>
       <c r="AY2" t="n">
-        <v>45.8</v>
+        <v>47.94</v>
       </c>
       <c r="AZ2" t="n">
         <v>16.26</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.5865748</v>
+        <v>2.5405037</v>
       </c>
       <c r="BB2" t="n">
-        <v>35.3968</v>
+        <v>39.9748</v>
       </c>
       <c r="BC2" t="n">
-        <v>24.7766</v>
+        <v>26.72135</v>
       </c>
       <c r="BD2" t="n">
         <v>0.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.008748907</v>
+        <v>0.008865247999999999</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -4339,7 +4525,7 @@
         <v>0</v>
       </c>
       <c r="BH2" t="n">
-        <v>3039384832</v>
+        <v>2869635328</v>
       </c>
       <c r="BI2" t="n">
         <v>0.07615</v>
@@ -4354,7 +4540,7 @@
         <v>0.11</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.53497005</v>
+        <v>0.54513</v>
       </c>
       <c r="BN2" t="n">
         <v>57238115</v>
@@ -4363,7 +4549,7 @@
         <v>17.741</v>
       </c>
       <c r="BP2" t="n">
-        <v>2.6582494</v>
+        <v>2.6109014</v>
       </c>
       <c r="BQ2" t="n">
         <v>1767139200</v>
@@ -4381,19 +4567,19 @@
         <v>76381000</v>
       </c>
       <c r="BV2" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.912</v>
+        <v>2.75</v>
       </c>
       <c r="BX2" t="n">
-        <v>16.433</v>
+        <v>15.515</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.3918283</v>
+        <v>1.3136864</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="CA2" t="n">
         <v>0.4</v>
@@ -4407,7 +4593,7 @@
         </is>
       </c>
       <c r="CD2" t="n">
-        <v>47.16</v>
+        <v>46.32</v>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
@@ -4511,142 +4697,142 @@
       </c>
       <c r="DG2" t="inlineStr">
         <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
+        <v>2.6595762</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>46.32</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>finmb_433420</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DM2" t="n">
+        <v>1781853919</v>
+      </c>
+      <c r="DN2" t="inlineStr">
         <is>
           <t>Europe/Rome</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DO2" t="inlineStr">
         <is>
           <t>CEST</t>
         </is>
       </c>
-      <c r="DK2" t="n">
+      <c r="DP2" t="n">
         <v>7200000</v>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>it_market</t>
         </is>
       </c>
-      <c r="DM2" t="b">
+      <c r="DR2" t="b">
         <v>0</v>
       </c>
-      <c r="DN2" t="n">
-        <v>3.1496034</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>47.16</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>11.763199</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0.3323238</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>22.3834</v>
-      </c>
       <c r="DS2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>6.3451996</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.15872999</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>19.59865</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.73344535</v>
+      </c>
+      <c r="DX2" t="n">
         <v>20</v>
       </c>
-      <c r="DT2" t="n">
+      <c r="DY2" t="n">
         <v>15</v>
       </c>
-      <c r="DU2" t="b">
+      <c r="DZ2" t="b">
         <v>0</v>
       </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DW2" t="b">
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>JENOPTIK</t>
+        </is>
+      </c>
+      <c r="EB2" t="b">
         <v>0</v>
       </c>
-      <c r="DX2" t="n">
+      <c r="EC2" t="n">
         <v>1703059200000</v>
       </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1780412731</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>1.4399986</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>47.06 - 47.06</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
+      <c r="ED2" t="n">
+        <v>1.2000008</v>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>45.28 - 45.28</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
         <is>
           <t>Milan</t>
         </is>
       </c>
-      <c r="ED2" t="n">
-        <v>109</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>30.83</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1.8879364</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>16.33 - 47.06</t>
-        </is>
+      <c r="EG2" t="n">
+        <v>119</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.099998474</v>
+        <v>29.99</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.0021249144</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>139.18283</v>
+        <v>1.8364972</v>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>16.33 - 47.94</t>
+        </is>
       </c>
       <c r="EK2" t="n">
+        <v>-1.6199989</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>-0.03379222</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>131.36864</v>
+      </c>
+      <c r="EN2" t="n">
         <v>1786548600</v>
       </c>
-      <c r="EL2" t="n">
+      <c r="EO2" t="n">
         <v>1786548600</v>
       </c>
-      <c r="EM2" t="n">
+      <c r="EP2" t="n">
         <v>1786548600</v>
       </c>
-      <c r="EN2" t="n">
+      <c r="EQ2" t="n">
         <v>1747133940</v>
       </c>
-      <c r="EO2" t="n">
+      <c r="ER2" t="n">
         <v>1747133940</v>
       </c>
-      <c r="EP2" t="b">
+      <c r="ES2" t="b">
         <v>0</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>0.9034089</v>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>JENOPTIK</t>
-        </is>
       </c>
       <c r="ET2" t="inlineStr"/>
     </row>
